--- a/grain_size/violin_descriptive_stats.xlsx
+++ b/grain_size/violin_descriptive_stats.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <t>count</t>
   </si>
@@ -28,27 +28,30 @@
     <t>min</t>
   </si>
   <si>
-    <t>25%</t>
-  </si>
-  <si>
-    <t>50%</t>
-  </si>
-  <si>
-    <t>75%</t>
+    <t>median</t>
   </si>
   <si>
     <t>max</t>
   </si>
   <si>
+    <t>Sample</t>
+  </si>
+  <si>
+    <t>71923A</t>
+  </si>
+  <si>
     <t>71923B</t>
   </si>
   <si>
-    <t>71923A</t>
-  </si>
-  <si>
     <t>80823A</t>
   </si>
   <si>
+    <t>83123A</t>
+  </si>
+  <si>
+    <t>90423A</t>
+  </si>
+  <si>
     <t>111123A</t>
   </si>
   <si>
@@ -56,12 +59,6 @@
   </si>
   <si>
     <t>LPSC</t>
-  </si>
-  <si>
-    <t>83123A</t>
-  </si>
-  <si>
-    <t>90423A</t>
   </si>
   <si>
     <t>LPNS</t>
@@ -422,10 +419,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:7">
+      <c r="A1" s="1" t="s">
+        <v>6</v>
+      </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -444,74 +444,56 @@
       <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:9">
-      <c r="A2" s="1" t="s">
+      <c r="B2">
+        <v>111</v>
+      </c>
+      <c r="C2">
+        <v>423</v>
+      </c>
+      <c r="D2">
+        <v>126</v>
+      </c>
+      <c r="E2">
+        <v>150</v>
+      </c>
+      <c r="F2">
+        <v>420</v>
+      </c>
+      <c r="G2">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B2">
+      <c r="B3">
         <v>98</v>
       </c>
-      <c r="C2">
+      <c r="C3">
         <v>21</v>
       </c>
-      <c r="D2">
+      <c r="D3">
         <v>7</v>
       </c>
-      <c r="E2">
+      <c r="E3">
         <v>8</v>
       </c>
-      <c r="F2">
-        <v>15</v>
-      </c>
-      <c r="G2">
+      <c r="F3">
         <v>19</v>
       </c>
-      <c r="H2">
-        <v>25</v>
-      </c>
-      <c r="I2">
+      <c r="G3">
         <v>39</v>
       </c>
     </row>
-    <row r="3" spans="1:9">
-      <c r="A3" s="1" t="s">
+    <row r="4" spans="1:7">
+      <c r="A4" s="1" t="s">
         <v>9</v>
-      </c>
-      <c r="B3">
-        <v>111</v>
-      </c>
-      <c r="C3">
-        <v>423</v>
-      </c>
-      <c r="D3">
-        <v>126</v>
-      </c>
-      <c r="E3">
-        <v>150</v>
-      </c>
-      <c r="F3">
-        <v>330</v>
-      </c>
-      <c r="G3">
-        <v>420</v>
-      </c>
-      <c r="H3">
-        <v>510</v>
-      </c>
-      <c r="I3">
-        <v>780</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9">
-      <c r="A4" s="1" t="s">
-        <v>10</v>
       </c>
       <c r="B4">
         <v>102</v>
@@ -526,166 +508,130 @@
         <v>18</v>
       </c>
       <c r="F4">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="G4">
-        <v>43</v>
-      </c>
-      <c r="H4">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5">
+        <v>89</v>
+      </c>
+      <c r="C5">
+        <v>95</v>
+      </c>
+      <c r="D5">
         <v>52</v>
       </c>
-      <c r="I4">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9">
-      <c r="A5" s="1" t="s">
+      <c r="E5">
+        <v>23</v>
+      </c>
+      <c r="F5">
+        <v>79</v>
+      </c>
+      <c r="G5">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B5">
+      <c r="B6">
+        <v>90</v>
+      </c>
+      <c r="C6">
+        <v>48</v>
+      </c>
+      <c r="D6">
+        <v>46</v>
+      </c>
+      <c r="E6">
+        <v>12</v>
+      </c>
+      <c r="F6">
+        <v>33</v>
+      </c>
+      <c r="G6">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7">
         <v>40</v>
       </c>
-      <c r="C5">
+      <c r="C7">
         <v>19</v>
       </c>
-      <c r="D5">
+      <c r="D7">
         <v>6</v>
       </c>
-      <c r="E5">
+      <c r="E7">
         <v>10</v>
       </c>
-      <c r="F5">
+      <c r="F7">
+        <v>19</v>
+      </c>
+      <c r="G7">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8">
+        <v>65</v>
+      </c>
+      <c r="C8">
+        <v>127</v>
+      </c>
+      <c r="D8">
+        <v>48</v>
+      </c>
+      <c r="E8">
+        <v>56</v>
+      </c>
+      <c r="F8">
+        <v>121</v>
+      </c>
+      <c r="G8">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9">
+        <v>84</v>
+      </c>
+      <c r="C9">
+        <v>115</v>
+      </c>
+      <c r="D9">
+        <v>29</v>
+      </c>
+      <c r="E9">
+        <v>42</v>
+      </c>
+      <c r="F9">
+        <v>113</v>
+      </c>
+      <c r="G9">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" s="1" t="s">
         <v>15</v>
-      </c>
-      <c r="G5">
-        <v>19</v>
-      </c>
-      <c r="H5">
-        <v>23</v>
-      </c>
-      <c r="I5">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9">
-      <c r="A6" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6">
-        <v>65</v>
-      </c>
-      <c r="C6">
-        <v>127</v>
-      </c>
-      <c r="D6">
-        <v>48</v>
-      </c>
-      <c r="E6">
-        <v>56</v>
-      </c>
-      <c r="F6">
-        <v>96</v>
-      </c>
-      <c r="G6">
-        <v>121</v>
-      </c>
-      <c r="H6">
-        <v>140</v>
-      </c>
-      <c r="I6">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9">
-      <c r="A7" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B7">
-        <v>84</v>
-      </c>
-      <c r="C7">
-        <v>115</v>
-      </c>
-      <c r="D7">
-        <v>29</v>
-      </c>
-      <c r="E7">
-        <v>42</v>
-      </c>
-      <c r="F7">
-        <v>94</v>
-      </c>
-      <c r="G7">
-        <v>113</v>
-      </c>
-      <c r="H7">
-        <v>132</v>
-      </c>
-      <c r="I7">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9">
-      <c r="A8" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8">
-        <v>89</v>
-      </c>
-      <c r="C8">
-        <v>95</v>
-      </c>
-      <c r="D8">
-        <v>52</v>
-      </c>
-      <c r="E8">
-        <v>23</v>
-      </c>
-      <c r="F8">
-        <v>62</v>
-      </c>
-      <c r="G8">
-        <v>79</v>
-      </c>
-      <c r="H8">
-        <v>111</v>
-      </c>
-      <c r="I8">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9">
-      <c r="A9" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B9">
-        <v>90</v>
-      </c>
-      <c r="C9">
-        <v>48</v>
-      </c>
-      <c r="D9">
-        <v>46</v>
-      </c>
-      <c r="E9">
-        <v>12</v>
-      </c>
-      <c r="F9">
-        <v>28</v>
-      </c>
-      <c r="G9">
-        <v>33</v>
-      </c>
-      <c r="H9">
-        <v>49</v>
-      </c>
-      <c r="I9">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9">
-      <c r="A10" s="1" t="s">
-        <v>16</v>
       </c>
       <c r="B10">
         <v>43</v>
@@ -700,15 +646,9 @@
         <v>49</v>
       </c>
       <c r="F10">
-        <v>97</v>
+        <v>153</v>
       </c>
       <c r="G10">
-        <v>153</v>
-      </c>
-      <c r="H10">
-        <v>326</v>
-      </c>
-      <c r="I10">
         <v>2898</v>
       </c>
     </row>
